--- a/题库/PY程序设计模拟题2.xlsx
+++ b/题库/PY程序设计模拟题2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="132">
   <si>
     <t>题号</t>
   </si>
@@ -103,16 +103,23 @@
     <t>以下选项的代码，执行后返回结果不是1,2,3的是()。</t>
   </si>
   <si>
-    <t>for i in range(3): print(i)</t>
-  </si>
-  <si>
-    <t>for i in range(3): print(i+1)</t>
-  </si>
-  <si>
-    <t>List=[1,2,3]; for i in List: print(i)</t>
-  </si>
-  <si>
-    <t>i=1; while i&lt;=3: print(i); i+=1</t>
+    <t>for i in range(3): 
+  print(i)</t>
+  </si>
+  <si>
+    <t>for i in range(3): 
+  print(i+1)</t>
+  </si>
+  <si>
+    <t>List=[1,2,3]; 
+for i in List: 
+  print(i)</t>
+  </si>
+  <si>
+    <t>i=1; 
+while i&lt;=3: 
+  print(i); 
+  i+=1</t>
   </si>
   <si>
     <t>下列关于字典的定义，（ ）是错误的。</t>
@@ -229,10 +236,16 @@
     <t>语句x=input()执行时，如果从键盘输入12并按回车键，则x的值是（）。</t>
   </si>
   <si>
+    <t>le2</t>
+  </si>
+  <si>
     <t>12'</t>
   </si>
   <si>
-    <t>x1 = (x2 + 1) * 2; x2 = x1; print(x1) （注：原题未给x2初始值，根据常见题库推测x2初始为22）</t>
+    <t xml:space="preserve"> x1 = (x2 + 1) * 2; 
+ x2 = x1; 
+print(x1) 
+（注：x2初始为22）</t>
   </si>
   <si>
     <t>以下选项描述正确的是（）。</t>
@@ -250,7 +263,9 @@
     <t>条件35&lt;=45&lt;75是合法的，且输出为False</t>
   </si>
   <si>
-    <t>下面代码的输出结果是（）。 s = "The python language is a cross platform language."; print(s.find('language', 30))</t>
+    <t>下面代码的输出结果是（）。 
+s = "The python language is a cross platform language.";
+ print(s.find('language', 30))</t>
   </si>
   <si>
     <t>系统报错</t>
@@ -277,7 +292,8 @@
     <t>表达式 “2 in [1,2,3,4]” 的值是【1】，max((1,2,3)*2)的值是【2】。</t>
   </si>
   <si>
-    <t>True; 3</t>
+    <t>True;
+3</t>
   </si>
   <si>
     <t>表达式set([1,1,2,3])的值为【1】。</t>
@@ -421,6 +437,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t>[1</t>
     </r>
     <r>
@@ -578,11 +600,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1220,11 +1243,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1662,7 +1691,7 @@
       </c>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" ht="56" spans="1:10">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1672,16 +1701,16 @@
       <c r="C5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="H5" s="1" t="s">
@@ -1915,14 +1944,14 @@
       <c r="D13" s="1">
         <v>12</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="3">
         <v>12</v>
       </c>
-      <c r="F13" s="2">
-        <v>100</v>
-      </c>
-      <c r="G13" s="5" t="s">
+      <c r="F13" s="4" t="s">
         <v>66</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>44</v>
@@ -1932,15 +1961,15 @@
       </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" ht="56" spans="1:10">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>67</v>
+      <c r="C14" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="D14" s="1">
         <v>46</v>
@@ -1970,19 +1999,19 @@
         <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>33</v>
@@ -1992,21 +2021,21 @@
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" ht="56" spans="1:10">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>73</v>
+      <c r="C16" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="D16" s="1">
         <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F16" s="1">
         <v>10</v>
@@ -2030,19 +2059,19 @@
         <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>44</v>
@@ -2054,7 +2083,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -2066,22 +2095,22 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" ht="28" spans="1:10">
       <c r="A19" s="1">
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
-      <c r="H19" s="1" t="s">
-        <v>82</v>
+      <c r="H19" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="I19" s="1">
         <v>2</v>
@@ -2093,17 +2122,17 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I20" s="1">
         <v>2</v>
@@ -2115,10 +2144,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -2137,17 +2166,17 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I22" s="1">
         <v>2</v>
@@ -2159,10 +2188,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -2181,10 +2210,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -2203,17 +2232,17 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I25" s="1">
         <v>2</v>
@@ -2225,17 +2254,17 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I26" s="1">
         <v>2</v>
@@ -2247,17 +2276,17 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I27" s="1">
         <v>2</v>
@@ -2269,10 +2298,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -2291,17 +2320,17 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I29" s="1">
         <v>2</v>
@@ -2313,17 +2342,17 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I30" s="1">
         <v>2</v>
@@ -2335,17 +2364,17 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="5" t="s">
-        <v>102</v>
+      <c r="H31" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="I31" s="1">
         <v>2</v>
@@ -2357,17 +2386,17 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I32" s="1">
         <v>2</v>
@@ -2379,17 +2408,17 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I33" s="1">
         <v>2</v>
@@ -2398,7 +2427,7 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2415,16 +2444,16 @@
         <v>31</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -2441,16 +2470,16 @@
         <v>32</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -2467,16 +2496,16 @@
         <v>33</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -2493,16 +2522,16 @@
         <v>34</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -2519,16 +2548,16 @@
         <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -2545,16 +2574,16 @@
         <v>36</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -2571,16 +2600,16 @@
         <v>37</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -2597,16 +2626,16 @@
         <v>38</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -2623,16 +2652,16 @@
         <v>39</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -2649,16 +2678,16 @@
         <v>40</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -2672,7 +2701,7 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2689,23 +2718,23 @@
         <v>41</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
-      <c r="H46" s="3" t="s">
-        <v>122</v>
+      <c r="H46" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="I46" s="1">
         <v>10</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" ht="28" spans="1:10">
@@ -2713,28 +2742,28 @@
         <v>42</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
-      <c r="H47" s="3" t="s">
-        <v>125</v>
+      <c r="H47" s="5" t="s">
+        <v>126</v>
       </c>
       <c r="I47" s="1">
         <v>10</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2751,23 +2780,23 @@
         <v>43</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="4" t="s">
-        <v>129</v>
+      <c r="H49" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="I49" s="1">
         <v>10</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/题库/PY程序设计模拟题2.xlsx
+++ b/题库/PY程序设计模拟题2.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="133">
   <si>
     <t>题号</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>语句x=input()执行时，如果从键盘输入12并按回车键，则x的值是（）。</t>
+  </si>
+  <si>
+    <t>12.0</t>
   </si>
   <si>
     <t>le2</t>
@@ -600,12 +603,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1243,7 +1245,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1253,14 +1255,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1944,14 +1943,14 @@
       <c r="D13" s="1">
         <v>12</v>
       </c>
-      <c r="E13" s="3">
-        <v>12</v>
+      <c r="E13" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13" s="7" t="s">
         <v>67</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>44</v>
@@ -1969,7 +1968,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" s="1">
         <v>46</v>
@@ -1999,19 +1998,19 @@
         <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>33</v>
@@ -2029,13 +2028,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D16" s="1">
         <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F16" s="1">
         <v>10</v>
@@ -2059,19 +2058,19 @@
         <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>44</v>
@@ -2083,7 +2082,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -2100,17 +2099,17 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I19" s="1">
         <v>2</v>
@@ -2122,17 +2121,17 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I20" s="1">
         <v>2</v>
@@ -2144,10 +2143,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -2166,17 +2165,17 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I22" s="1">
         <v>2</v>
@@ -2188,10 +2187,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -2210,10 +2209,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -2232,17 +2231,17 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I25" s="1">
         <v>2</v>
@@ -2254,17 +2253,17 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I26" s="1">
         <v>2</v>
@@ -2276,17 +2275,17 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I27" s="1">
         <v>2</v>
@@ -2298,10 +2297,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -2320,17 +2319,17 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I29" s="1">
         <v>2</v>
@@ -2342,17 +2341,17 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I30" s="1">
         <v>2</v>
@@ -2364,17 +2363,17 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="7" t="s">
-        <v>103</v>
+      <c r="H31" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="I31" s="1">
         <v>2</v>
@@ -2386,17 +2385,17 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I32" s="1">
         <v>2</v>
@@ -2408,17 +2407,17 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I33" s="1">
         <v>2</v>
@@ -2427,7 +2426,7 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2444,16 +2443,16 @@
         <v>31</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -2470,16 +2469,16 @@
         <v>32</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -2496,16 +2495,16 @@
         <v>33</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -2522,16 +2521,16 @@
         <v>34</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -2548,16 +2547,16 @@
         <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -2574,16 +2573,16 @@
         <v>36</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -2600,16 +2599,16 @@
         <v>37</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -2626,16 +2625,16 @@
         <v>38</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -2652,16 +2651,16 @@
         <v>39</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -2678,16 +2677,16 @@
         <v>40</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -2701,7 +2700,7 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2718,23 +2717,23 @@
         <v>41</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
-      <c r="H46" s="5" t="s">
-        <v>123</v>
+      <c r="H46" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="I46" s="1">
         <v>10</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" ht="28" spans="1:10">
@@ -2742,28 +2741,28 @@
         <v>42</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
-      <c r="H47" s="5" t="s">
-        <v>126</v>
+      <c r="H47" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="I47" s="1">
         <v>10</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2780,23 +2779,23 @@
         <v>43</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="6" t="s">
-        <v>130</v>
+      <c r="H49" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="I49" s="1">
         <v>10</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/题库/PY程序设计模拟题2.xlsx
+++ b/题库/PY程序设计模拟题2.xlsx
@@ -356,7 +356,7 @@
     <t>表达式str([1, 2, 3])的值为【1】。</t>
   </si>
   <si>
-    <t>[1, 2, 3]'</t>
+    <t>"[1, 2, 3]"</t>
   </si>
   <si>
     <t>判断n是偶数的Python表达式应为【1】。</t>
@@ -2372,7 +2372,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="6" t="s">
+      <c r="H31" s="3" t="s">
         <v>104</v>
       </c>
       <c r="I31" s="1">
